--- a/artfynd/A 9956-2022 artfynd.xlsx
+++ b/artfynd/A 9956-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9956-2022 artfynd.xlsx
+++ b/artfynd/A 9956-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,132 +902,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>68752585</v>
-      </c>
-      <c r="B4" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Högbyn, ca 300 m V parkeringen (ögonpyrola), Vstm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>539558.3840955605</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6647183.363519855</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Fagersta</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Fagersta</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>U-Fag-0209</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2016-06-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2016-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fuktig stigkant vid bäck i skogen, tätt bestånd på ett par kvadratmeter. Även spridd glesare längs  stigens kanter.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Einar Marklund</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Anders Jacobson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9956-2022 artfynd.xlsx
+++ b/artfynd/A 9956-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60190061</v>
+        <v>60190070</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539557.8878126596</v>
+        <v>539558</v>
       </c>
       <c r="R2" t="n">
-        <v>6647182.857353433</v>
+        <v>6647183</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,24 +743,9 @@
           <t>2016-06-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tätt bestånd på ett par kvadratmeter. Även spridd glesare längs några meter av stigens N kant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60190070</v>
+        <v>60190061</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539557.8878126596</v>
+        <v>539558</v>
       </c>
       <c r="R3" t="n">
-        <v>6647182.857353433</v>
+        <v>6647183</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +840,14 @@
           <t>2016-06-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-06-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tätt bestånd på ett par kvadratmeter. Även spridd glesare längs några meter av stigens N kant.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9956-2022 artfynd.xlsx
+++ b/artfynd/A 9956-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60190070</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,8 +881,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60190061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>